--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8075E0FA-F368-45F3-A6F6-1AFD783085DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D6A04E-F425-4A58-AEBD-B909D775C5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="4" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -21,8 +21,9 @@
     <sheet name="Creation" sheetId="1" r:id="rId6"/>
     <sheet name="Form Fields 1" sheetId="4" r:id="rId7"/>
     <sheet name="Edition" sheetId="2" r:id="rId8"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId9"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId10"/>
+    <sheet name="Grantee_Edition" sheetId="11" r:id="rId9"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId11"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="93">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -286,6 +287,33 @@
   </si>
   <si>
     <t>City__c</t>
+  </si>
+  <si>
+    <t>DUNS__c</t>
+  </si>
+  <si>
+    <t>YRNMVN96JC17</t>
+  </si>
+  <si>
+    <t>Victor EXE</t>
+  </si>
+  <si>
+    <t>Automation Test</t>
+  </si>
+  <si>
+    <t>Detailed Line Item Budget</t>
+  </si>
+  <si>
+    <t>AOR_Contact__c</t>
+  </si>
+  <si>
+    <t>BudgetLevel__c</t>
+  </si>
+  <si>
+    <t>Congressionaldistrict__c</t>
+  </si>
+  <si>
+    <t>1st District</t>
   </si>
 </sst>
 </file>
@@ -342,7 +370,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -353,6 +381,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -372,9 +403,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -412,7 +443,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -518,7 +549,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -660,7 +691,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -669,11 +700,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -749,12 +780,159 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -820,10 +998,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -900,10 +1078,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -948,10 +1126,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1116,10 +1294,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1277,10 +1455,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1313,10 +1491,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1361,10 +1539,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1451,12 +1629,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579718D7-4C36-4B54-B5F7-43B2B7C68B72}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1466,133 +1644,77 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D6A04E-F425-4A58-AEBD-B909D775C5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B13B1A-CE7E-4AAF-BDEF-245531449844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="4" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -22,8 +22,9 @@
     <sheet name="Form Fields 1" sheetId="4" r:id="rId7"/>
     <sheet name="Edition" sheetId="2" r:id="rId8"/>
     <sheet name="Grantee_Edition" sheetId="11" r:id="rId9"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId11"/>
+    <sheet name="Grantee_PreApp_Edition" sheetId="12" r:id="rId10"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId12"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="93">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -780,6 +781,86 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1B012E-3E50-42EE-91DF-D3E937268BB4}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="23.21875" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -926,7 +1007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B13B1A-CE7E-4AAF-BDEF-245531449844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DA0586-738A-4E33-801A-E8E41F39922B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="93">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -782,7 +782,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1B012E-3E50-42EE-91DF-D3E937268BB4}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="23.21875" customWidth="1"/>
@@ -835,23 +835,12 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" t="s">
         <v>88</v>
       </c>
     </row>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DA0586-738A-4E33-801A-E8E41F39922B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E62A84-0DC7-4704-8A2E-9972CE3590AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="94">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>1st District</t>
+  </si>
+  <si>
+    <t>BudgetBuildupNeeded__c</t>
   </si>
 </sst>
 </file>
@@ -838,7 +841,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
         <v>88</v>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77397491-AFBC-4396-85B5-E90B7DB70698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7DC602-6B01-4087-ABA4-798EAD15EA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="6" activeTab="10" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -23,8 +23,9 @@
     <sheet name="Edition" sheetId="2" r:id="rId8"/>
     <sheet name="Grantee_Edition" sheetId="11" r:id="rId9"/>
     <sheet name="Grantee_PreApp_Edition" sheetId="12" r:id="rId10"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId11"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId12"/>
+    <sheet name="Grantee_SF-LLL_Form_Valid" sheetId="13" r:id="rId11"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId12"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId13"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="190">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -318,13 +319,301 @@
   </si>
   <si>
     <t>BudgetBuildupNeeded__c</t>
+  </si>
+  <si>
+    <t>TypeOfFederalAction__c</t>
+  </si>
+  <si>
+    <t>StatusOfFederalAction__c</t>
+  </si>
+  <si>
+    <t>ReportType__c</t>
+  </si>
+  <si>
+    <t>MaterialChangeYear__c</t>
+  </si>
+  <si>
+    <t>MaterialChangeQuarter__c</t>
+  </si>
+  <si>
+    <t>DateOfLastReport__c</t>
+  </si>
+  <si>
+    <t>TypeOfReportingEntity__c</t>
+  </si>
+  <si>
+    <t>Tier__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_Organization_Name__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_Street_1__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_Street_2__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_City__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_State__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>PrimeSubawardeeCongressionalDistrict__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_Name__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_Street_1__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_Street_2__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_City__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_State__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>PrimeCongressionalDistrict__c</t>
+  </si>
+  <si>
+    <t>Federal_Department_Agency__c</t>
+  </si>
+  <si>
+    <t>CFDA_Program_Title__c</t>
+  </si>
+  <si>
+    <t>CFDA_Number__c</t>
+  </si>
+  <si>
+    <t>FederalActionNumber__c</t>
+  </si>
+  <si>
+    <t>Award_Amount__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Prefix__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_First_Name__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Last_Name__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Suffix__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Street_1__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Street_2__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_City__c</t>
+  </si>
+  <si>
+    <t>State2__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>Individual_Prefix__c</t>
+  </si>
+  <si>
+    <t>Individual_First_Name__c</t>
+  </si>
+  <si>
+    <t>Individual_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Individual_Last_Name__c</t>
+  </si>
+  <si>
+    <t>Individual_Suffix__c</t>
+  </si>
+  <si>
+    <t>Individual_Street_1__c</t>
+  </si>
+  <si>
+    <t>Individual_Street_2__c</t>
+  </si>
+  <si>
+    <t>Individual_City__c</t>
+  </si>
+  <si>
+    <t>State3__c</t>
+  </si>
+  <si>
+    <t>Individual_Zip__c</t>
+  </si>
+  <si>
+    <t>AORSignature__c</t>
+  </si>
+  <si>
+    <t>Signature_Prefix__c</t>
+  </si>
+  <si>
+    <t>Signature_First_Name__c</t>
+  </si>
+  <si>
+    <t>Signature_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Signature_Last_Name__c</t>
+  </si>
+  <si>
+    <t>Signature_Suffix__c</t>
+  </si>
+  <si>
+    <t>Signature_Title__c</t>
+  </si>
+  <si>
+    <t>Signature_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>Signature_Date__c</t>
+  </si>
+  <si>
+    <t>1 St Tier</t>
+  </si>
+  <si>
+    <t>Austin Lee</t>
+  </si>
+  <si>
+    <t>Howard</t>
+  </si>
+  <si>
+    <t>Lane 2</t>
+  </si>
+  <si>
+    <t>Califonia</t>
+  </si>
+  <si>
+    <t>AK: Alaska</t>
+  </si>
+  <si>
+    <t>12345-1234</t>
+  </si>
+  <si>
+    <t>James Anderson</t>
+  </si>
+  <si>
+    <t>Street 4</t>
+  </si>
+  <si>
+    <t>Lane 1</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>AL: Alabama</t>
+  </si>
+  <si>
+    <t>23467-8905</t>
+  </si>
+  <si>
+    <t>State of Agency</t>
+  </si>
+  <si>
+    <t>Automation Test Program</t>
+  </si>
+  <si>
+    <t>Award-123-456</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Christi</t>
+  </si>
+  <si>
+    <t>Jr.</t>
+  </si>
+  <si>
+    <t>Street Road</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>AR: Arkansas</t>
+  </si>
+  <si>
+    <t>4673-907</t>
+  </si>
+  <si>
+    <t>Simon</t>
+  </si>
+  <si>
+    <t>Jackes</t>
+  </si>
+  <si>
+    <t>Street 1</t>
+  </si>
+  <si>
+    <t>Street 2</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>CA: California</t>
+  </si>
+  <si>
+    <t>34789-234</t>
+  </si>
+  <si>
+    <t>Grantee PO</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Merry</t>
+  </si>
+  <si>
+    <t>Sr.</t>
+  </si>
+  <si>
+    <t>SubAwardee</t>
+  </si>
+  <si>
+    <t>Grant</t>
+  </si>
+  <si>
+    <t>InitialAward</t>
+  </si>
+  <si>
+    <t>material change</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +641,12 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -374,7 +669,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -388,6 +683,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -853,6 +1149,647 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67079260-A8F8-4A08-88D9-C04C84F847B8}">
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26">
+        <v>11.122999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C56">
+        <v>8906784590</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -999,7 +1936,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7DC602-6B01-4087-ABA4-798EAD15EA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC75D24E-13DC-40C0-986D-41C88B5D527E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="6" activeTab="10" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -24,8 +24,9 @@
     <sheet name="Grantee_Edition" sheetId="11" r:id="rId9"/>
     <sheet name="Grantee_PreApp_Edition" sheetId="12" r:id="rId10"/>
     <sheet name="Grantee_SF-LLL_Form_Valid" sheetId="13" r:id="rId11"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId12"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId13"/>
+    <sheet name="SF424_FORM" sheetId="14" r:id="rId12"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId14"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="246">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -607,13 +608,181 @@
   </si>
   <si>
     <t>material change</t>
+  </si>
+  <si>
+    <t>SubmissionType__c</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>ApplicationType__c</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>LegalName__c</t>
+  </si>
+  <si>
+    <t>SAMUEI__c</t>
+  </si>
+  <si>
+    <t>Street__c</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>Country__c</t>
+  </si>
+  <si>
+    <t>USA: UNITED STATES</t>
+  </si>
+  <si>
+    <t>Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>POC Prefix</t>
+  </si>
+  <si>
+    <t>POC_First_Name__c</t>
+  </si>
+  <si>
+    <t>POC_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>POC_Last_Name__c</t>
+  </si>
+  <si>
+    <t>Mathews</t>
+  </si>
+  <si>
+    <t>POC_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>(023) 479-9100</t>
+  </si>
+  <si>
+    <t>POC_Email__c</t>
+  </si>
+  <si>
+    <t>automationspi1@yopmail.com</t>
+  </si>
+  <si>
+    <t>ApplicantType1__c</t>
+  </si>
+  <si>
+    <t>B: County Government</t>
+  </si>
+  <si>
+    <t>OtherApplicantType__c</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>NameofFederalAgency__c</t>
+  </si>
+  <si>
+    <t>FederalAgency</t>
+  </si>
+  <si>
+    <t>FundingOpportunityTitle__c</t>
+  </si>
+  <si>
+    <t>DescriptiveTitleOfProject__c</t>
+  </si>
+  <si>
+    <t>ApplicantDistrict__c</t>
+  </si>
+  <si>
+    <t>ProgramDistrict__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>FederalFunding__c</t>
+  </si>
+  <si>
+    <t>ApplicantFunding__c</t>
+  </si>
+  <si>
+    <t>StateFunding__c</t>
+  </si>
+  <si>
+    <t>LocalFunding__c</t>
+  </si>
+  <si>
+    <t>OtherFunding__c</t>
+  </si>
+  <si>
+    <t>ProgramIncomeFunding__c</t>
+  </si>
+  <si>
+    <t>ApplicationReview__c</t>
+  </si>
+  <si>
+    <t>a. This application was made available to the State under the Executive Order 12372 Process for review on</t>
+  </si>
+  <si>
+    <t>FederalDebt__c</t>
+  </si>
+  <si>
+    <t>Agreement__c</t>
+  </si>
+  <si>
+    <t>checked</t>
+  </si>
+  <si>
+    <t>AOR_Prefix__c</t>
+  </si>
+  <si>
+    <t>AOR_First_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Last_Name__c</t>
+  </si>
+  <si>
+    <t>AOR Suffix</t>
+  </si>
+  <si>
+    <t>M.D.</t>
+  </si>
+  <si>
+    <t>AOR_Title__c</t>
+  </si>
+  <si>
+    <t>AOR_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>AOR_Email__c</t>
+  </si>
+  <si>
+    <t>AORDateSigned__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -647,6 +816,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -669,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -684,6 +859,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1790,6 +1967,530 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BAA1334-5A12-4B6F-A35F-258AF51C82C8}">
+  <dimension ref="A1:C46"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="89.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="9">
+        <v>123456789012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C27">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C30">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>229</v>
+      </c>
+      <c r="C32">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>230</v>
+      </c>
+      <c r="C33">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C34" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>236</v>
+      </c>
+      <c r="C37" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>238</v>
+      </c>
+      <c r="C39" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C41" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>245</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C16" r:id="rId1" xr:uid="{70903C96-5C84-4A2C-8D40-A45D77DEA303}"/>
+    <hyperlink ref="C44" r:id="rId2" xr:uid="{EA223F5E-0C67-458D-8B52-67B94FA99AD6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -1936,7 +2637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77397491-AFBC-4396-85B5-E90B7DB70698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC75D24E-13DC-40C0-986D-41C88B5D527E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -23,8 +23,10 @@
     <sheet name="Edition" sheetId="2" r:id="rId8"/>
     <sheet name="Grantee_Edition" sheetId="11" r:id="rId9"/>
     <sheet name="Grantee_PreApp_Edition" sheetId="12" r:id="rId10"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId11"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId12"/>
+    <sheet name="Grantee_SF-LLL_Form_Valid" sheetId="13" r:id="rId11"/>
+    <sheet name="SF424_FORM" sheetId="14" r:id="rId12"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId14"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="246">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -318,13 +320,469 @@
   </si>
   <si>
     <t>BudgetBuildupNeeded__c</t>
+  </si>
+  <si>
+    <t>TypeOfFederalAction__c</t>
+  </si>
+  <si>
+    <t>StatusOfFederalAction__c</t>
+  </si>
+  <si>
+    <t>ReportType__c</t>
+  </si>
+  <si>
+    <t>MaterialChangeYear__c</t>
+  </si>
+  <si>
+    <t>MaterialChangeQuarter__c</t>
+  </si>
+  <si>
+    <t>DateOfLastReport__c</t>
+  </si>
+  <si>
+    <t>TypeOfReportingEntity__c</t>
+  </si>
+  <si>
+    <t>Tier__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_Organization_Name__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_Street_1__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_Street_2__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_City__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_State__c</t>
+  </si>
+  <si>
+    <t>Reporting_Entity_Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>PrimeSubawardeeCongressionalDistrict__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_Name__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_Street_1__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_Street_2__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_City__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_State__c</t>
+  </si>
+  <si>
+    <t>Prime_Organization_Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>PrimeCongressionalDistrict__c</t>
+  </si>
+  <si>
+    <t>Federal_Department_Agency__c</t>
+  </si>
+  <si>
+    <t>CFDA_Program_Title__c</t>
+  </si>
+  <si>
+    <t>CFDA_Number__c</t>
+  </si>
+  <si>
+    <t>FederalActionNumber__c</t>
+  </si>
+  <si>
+    <t>Award_Amount__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Prefix__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_First_Name__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Last_Name__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Suffix__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Street_1__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Street_2__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_City__c</t>
+  </si>
+  <si>
+    <t>State2__c</t>
+  </si>
+  <si>
+    <t>Lobbying_Registrant_Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>Individual_Prefix__c</t>
+  </si>
+  <si>
+    <t>Individual_First_Name__c</t>
+  </si>
+  <si>
+    <t>Individual_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Individual_Last_Name__c</t>
+  </si>
+  <si>
+    <t>Individual_Suffix__c</t>
+  </si>
+  <si>
+    <t>Individual_Street_1__c</t>
+  </si>
+  <si>
+    <t>Individual_Street_2__c</t>
+  </si>
+  <si>
+    <t>Individual_City__c</t>
+  </si>
+  <si>
+    <t>State3__c</t>
+  </si>
+  <si>
+    <t>Individual_Zip__c</t>
+  </si>
+  <si>
+    <t>AORSignature__c</t>
+  </si>
+  <si>
+    <t>Signature_Prefix__c</t>
+  </si>
+  <si>
+    <t>Signature_First_Name__c</t>
+  </si>
+  <si>
+    <t>Signature_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Signature_Last_Name__c</t>
+  </si>
+  <si>
+    <t>Signature_Suffix__c</t>
+  </si>
+  <si>
+    <t>Signature_Title__c</t>
+  </si>
+  <si>
+    <t>Signature_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>Signature_Date__c</t>
+  </si>
+  <si>
+    <t>1 St Tier</t>
+  </si>
+  <si>
+    <t>Austin Lee</t>
+  </si>
+  <si>
+    <t>Howard</t>
+  </si>
+  <si>
+    <t>Lane 2</t>
+  </si>
+  <si>
+    <t>Califonia</t>
+  </si>
+  <si>
+    <t>AK: Alaska</t>
+  </si>
+  <si>
+    <t>12345-1234</t>
+  </si>
+  <si>
+    <t>James Anderson</t>
+  </si>
+  <si>
+    <t>Street 4</t>
+  </si>
+  <si>
+    <t>Lane 1</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>AL: Alabama</t>
+  </si>
+  <si>
+    <t>23467-8905</t>
+  </si>
+  <si>
+    <t>State of Agency</t>
+  </si>
+  <si>
+    <t>Automation Test Program</t>
+  </si>
+  <si>
+    <t>Award-123-456</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Christi</t>
+  </si>
+  <si>
+    <t>Jr.</t>
+  </si>
+  <si>
+    <t>Street Road</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>AR: Arkansas</t>
+  </si>
+  <si>
+    <t>4673-907</t>
+  </si>
+  <si>
+    <t>Simon</t>
+  </si>
+  <si>
+    <t>Jackes</t>
+  </si>
+  <si>
+    <t>Street 1</t>
+  </si>
+  <si>
+    <t>Street 2</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>CA: California</t>
+  </si>
+  <si>
+    <t>34789-234</t>
+  </si>
+  <si>
+    <t>Grantee PO</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Merry</t>
+  </si>
+  <si>
+    <t>Sr.</t>
+  </si>
+  <si>
+    <t>SubAwardee</t>
+  </si>
+  <si>
+    <t>Grant</t>
+  </si>
+  <si>
+    <t>InitialAward</t>
+  </si>
+  <si>
+    <t>material change</t>
+  </si>
+  <si>
+    <t>SubmissionType__c</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>ApplicationType__c</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>LegalName__c</t>
+  </si>
+  <si>
+    <t>SAMUEI__c</t>
+  </si>
+  <si>
+    <t>Street__c</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>Country__c</t>
+  </si>
+  <si>
+    <t>USA: UNITED STATES</t>
+  </si>
+  <si>
+    <t>Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>POC Prefix</t>
+  </si>
+  <si>
+    <t>POC_First_Name__c</t>
+  </si>
+  <si>
+    <t>POC_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>POC_Last_Name__c</t>
+  </si>
+  <si>
+    <t>Mathews</t>
+  </si>
+  <si>
+    <t>POC_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>(023) 479-9100</t>
+  </si>
+  <si>
+    <t>POC_Email__c</t>
+  </si>
+  <si>
+    <t>automationspi1@yopmail.com</t>
+  </si>
+  <si>
+    <t>ApplicantType1__c</t>
+  </si>
+  <si>
+    <t>B: County Government</t>
+  </si>
+  <si>
+    <t>OtherApplicantType__c</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>NameofFederalAgency__c</t>
+  </si>
+  <si>
+    <t>FederalAgency</t>
+  </si>
+  <si>
+    <t>FundingOpportunityTitle__c</t>
+  </si>
+  <si>
+    <t>DescriptiveTitleOfProject__c</t>
+  </si>
+  <si>
+    <t>ApplicantDistrict__c</t>
+  </si>
+  <si>
+    <t>ProgramDistrict__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>FederalFunding__c</t>
+  </si>
+  <si>
+    <t>ApplicantFunding__c</t>
+  </si>
+  <si>
+    <t>StateFunding__c</t>
+  </si>
+  <si>
+    <t>LocalFunding__c</t>
+  </si>
+  <si>
+    <t>OtherFunding__c</t>
+  </si>
+  <si>
+    <t>ProgramIncomeFunding__c</t>
+  </si>
+  <si>
+    <t>ApplicationReview__c</t>
+  </si>
+  <si>
+    <t>a. This application was made available to the State under the Executive Order 12372 Process for review on</t>
+  </si>
+  <si>
+    <t>FederalDebt__c</t>
+  </si>
+  <si>
+    <t>Agreement__c</t>
+  </si>
+  <si>
+    <t>checked</t>
+  </si>
+  <si>
+    <t>AOR_Prefix__c</t>
+  </si>
+  <si>
+    <t>AOR_First_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Last_Name__c</t>
+  </si>
+  <si>
+    <t>AOR Suffix</t>
+  </si>
+  <si>
+    <t>M.D.</t>
+  </si>
+  <si>
+    <t>AOR_Title__c</t>
+  </si>
+  <si>
+    <t>AOR_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>AOR_Email__c</t>
+  </si>
+  <si>
+    <t>AORDateSigned__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +810,18 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -374,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -388,6 +858,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -853,6 +1326,1171 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67079260-A8F8-4A08-88D9-C04C84F847B8}">
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26">
+        <v>11.122999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C56">
+        <v>8906784590</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BAA1334-5A12-4B6F-A35F-258AF51C82C8}">
+  <dimension ref="A1:C46"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="89.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="9">
+        <v>123456789012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C27">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C30">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>229</v>
+      </c>
+      <c r="C32">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>230</v>
+      </c>
+      <c r="C33">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C34" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>236</v>
+      </c>
+      <c r="C37" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>238</v>
+      </c>
+      <c r="C39" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C41" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>245</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C16" r:id="rId1" xr:uid="{70903C96-5C84-4A2C-8D40-A45D77DEA303}"/>
+    <hyperlink ref="C44" r:id="rId2" xr:uid="{EA223F5E-0C67-458D-8B52-67B94FA99AD6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -999,7 +2637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC75D24E-13DC-40C0-986D-41C88B5D527E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D9CBA5-221B-4558-9691-83A95C3241A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -649,9 +649,6 @@
     <t>Zip_Postal_Code__c</t>
   </si>
   <si>
-    <t>POC Prefix</t>
-  </si>
-  <si>
     <t>POC_First_Name__c</t>
   </si>
   <si>
@@ -760,9 +757,6 @@
     <t>AOR_Last_Name__c</t>
   </si>
   <si>
-    <t>AOR Suffix</t>
-  </si>
-  <si>
     <t>M.D.</t>
   </si>
   <si>
@@ -776,6 +770,12 @@
   </si>
   <si>
     <t>AORDateSigned__c</t>
+  </si>
+  <si>
+    <t>POC_Prefix__c</t>
+  </si>
+  <si>
+    <t>AOR_Suffix__c</t>
   </si>
 </sst>
 </file>
@@ -2090,7 +2090,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
         <v>166</v>
@@ -2101,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C12" t="s">
         <v>168</v>
@@ -2112,10 +2112,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" t="s">
         <v>205</v>
-      </c>
-      <c r="C13" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2123,10 +2123,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" t="s">
         <v>207</v>
-      </c>
-      <c r="C14" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2134,10 +2134,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" t="s">
         <v>209</v>
-      </c>
-      <c r="C15" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2145,10 +2145,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2156,10 +2156,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" t="s">
         <v>213</v>
-      </c>
-      <c r="C17" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" t="s">
         <v>215</v>
-      </c>
-      <c r="C18" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2178,10 +2178,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" t="s">
         <v>217</v>
-      </c>
-      <c r="C19" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2203,7 +2203,7 @@
         <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2211,10 +2211,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2222,10 +2222,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2233,10 +2233,10 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C24" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2244,10 +2244,10 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2255,7 +2255,7 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C27">
         <v>365</v>
@@ -2277,7 +2277,7 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C28">
         <v>10000</v>
@@ -2288,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C29">
         <v>10000</v>
@@ -2299,7 +2299,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C30">
         <v>10000</v>
@@ -2310,7 +2310,7 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C31">
         <v>10000</v>
@@ -2321,7 +2321,7 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C32">
         <v>10000</v>
@@ -2332,7 +2332,7 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C33">
         <v>10000</v>
@@ -2343,10 +2343,10 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
+        <v>230</v>
+      </c>
+      <c r="C34" t="s">
         <v>231</v>
-      </c>
-      <c r="C34" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2354,7 +2354,7 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C35" t="s">
         <v>35</v>
@@ -2365,10 +2365,10 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
+        <v>233</v>
+      </c>
+      <c r="C36" t="s">
         <v>234</v>
-      </c>
-      <c r="C36" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2376,7 +2376,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C37" t="s">
         <v>166</v>
@@ -2387,7 +2387,7 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C38" t="s">
         <v>168</v>
@@ -2398,10 +2398,10 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2409,10 +2409,10 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2420,10 +2420,10 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C41" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2431,10 +2431,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C42" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2442,10 +2442,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2453,10 +2453,10 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2467,7 +2467,7 @@
         <v>141</v>
       </c>
       <c r="C45" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2475,7 +2475,7 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C46">
         <v>0</v>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7DC602-6B01-4087-ABA4-798EAD15EA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D9CBA5-221B-4558-9691-83A95C3241A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="6" activeTab="10" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -24,8 +24,9 @@
     <sheet name="Grantee_Edition" sheetId="11" r:id="rId9"/>
     <sheet name="Grantee_PreApp_Edition" sheetId="12" r:id="rId10"/>
     <sheet name="Grantee_SF-LLL_Form_Valid" sheetId="13" r:id="rId11"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId12"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId13"/>
+    <sheet name="SF424_FORM" sheetId="14" r:id="rId12"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId14"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="246">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -607,13 +608,181 @@
   </si>
   <si>
     <t>material change</t>
+  </si>
+  <si>
+    <t>SubmissionType__c</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>ApplicationType__c</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>LegalName__c</t>
+  </si>
+  <si>
+    <t>SAMUEI__c</t>
+  </si>
+  <si>
+    <t>Street__c</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>Country__c</t>
+  </si>
+  <si>
+    <t>USA: UNITED STATES</t>
+  </si>
+  <si>
+    <t>Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>POC_First_Name__c</t>
+  </si>
+  <si>
+    <t>POC_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>POC_Last_Name__c</t>
+  </si>
+  <si>
+    <t>Mathews</t>
+  </si>
+  <si>
+    <t>POC_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>(023) 479-9100</t>
+  </si>
+  <si>
+    <t>POC_Email__c</t>
+  </si>
+  <si>
+    <t>automationspi1@yopmail.com</t>
+  </si>
+  <si>
+    <t>ApplicantType1__c</t>
+  </si>
+  <si>
+    <t>B: County Government</t>
+  </si>
+  <si>
+    <t>OtherApplicantType__c</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>NameofFederalAgency__c</t>
+  </si>
+  <si>
+    <t>FederalAgency</t>
+  </si>
+  <si>
+    <t>FundingOpportunityTitle__c</t>
+  </si>
+  <si>
+    <t>DescriptiveTitleOfProject__c</t>
+  </si>
+  <si>
+    <t>ApplicantDistrict__c</t>
+  </si>
+  <si>
+    <t>ProgramDistrict__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>FederalFunding__c</t>
+  </si>
+  <si>
+    <t>ApplicantFunding__c</t>
+  </si>
+  <si>
+    <t>StateFunding__c</t>
+  </si>
+  <si>
+    <t>LocalFunding__c</t>
+  </si>
+  <si>
+    <t>OtherFunding__c</t>
+  </si>
+  <si>
+    <t>ProgramIncomeFunding__c</t>
+  </si>
+  <si>
+    <t>ApplicationReview__c</t>
+  </si>
+  <si>
+    <t>a. This application was made available to the State under the Executive Order 12372 Process for review on</t>
+  </si>
+  <si>
+    <t>FederalDebt__c</t>
+  </si>
+  <si>
+    <t>Agreement__c</t>
+  </si>
+  <si>
+    <t>checked</t>
+  </si>
+  <si>
+    <t>AOR_Prefix__c</t>
+  </si>
+  <si>
+    <t>AOR_First_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Last_Name__c</t>
+  </si>
+  <si>
+    <t>M.D.</t>
+  </si>
+  <si>
+    <t>AOR_Title__c</t>
+  </si>
+  <si>
+    <t>AOR_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>AOR_Email__c</t>
+  </si>
+  <si>
+    <t>AORDateSigned__c</t>
+  </si>
+  <si>
+    <t>POC_Prefix__c</t>
+  </si>
+  <si>
+    <t>AOR_Suffix__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -647,6 +816,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -669,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -684,6 +859,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1790,6 +1967,530 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BAA1334-5A12-4B6F-A35F-258AF51C82C8}">
+  <dimension ref="A1:C46"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="89.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="9">
+        <v>123456789012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>218</v>
+      </c>
+      <c r="C22" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C25" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>224</v>
+      </c>
+      <c r="C28">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>225</v>
+      </c>
+      <c r="C29">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>229</v>
+      </c>
+      <c r="C33">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>230</v>
+      </c>
+      <c r="C34" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>232</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>233</v>
+      </c>
+      <c r="C36" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>235</v>
+      </c>
+      <c r="C37" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>236</v>
+      </c>
+      <c r="C38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>237</v>
+      </c>
+      <c r="C39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C43" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>242</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>243</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C16" r:id="rId1" xr:uid="{70903C96-5C84-4A2C-8D40-A45D77DEA303}"/>
+    <hyperlink ref="C44" r:id="rId2" xr:uid="{EA223F5E-0C67-458D-8B52-67B94FA99AD6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -1936,7 +2637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D9CBA5-221B-4558-9691-83A95C3241A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B62077-22A8-42B7-A065-D4237A93A44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -313,9 +313,6 @@
     <t>BudgetLevel__c</t>
   </si>
   <si>
-    <t>Congressionaldistrict__c</t>
-  </si>
-  <si>
     <t>1st District</t>
   </si>
   <si>
@@ -776,6 +773,9 @@
   </si>
   <si>
     <t>AOR_Suffix__c</t>
+  </si>
+  <si>
+    <t>CongressionalDistrict1__c</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1314,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
         <v>88</v>
@@ -1350,10 +1350,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1361,10 +1361,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1372,10 +1372,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1383,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5">
         <v>2023</v>
@@ -1394,7 +1394,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1405,7 +1405,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7">
         <v>-50</v>
@@ -1416,10 +1416,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1427,10 +1427,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1438,10 +1438,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1449,10 +1449,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1460,10 +1460,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1471,10 +1471,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1482,10 +1482,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1493,10 +1493,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1504,7 +1504,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C16">
         <v>123</v>
@@ -1515,10 +1515,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1526,10 +1526,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1537,10 +1537,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1548,10 +1548,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1559,10 +1559,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1570,10 +1570,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1581,7 +1581,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C23">
         <v>456</v>
@@ -1592,10 +1592,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1603,10 +1603,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1614,7 +1614,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C26">
         <v>11.122999999999999</v>
@@ -1625,10 +1625,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1636,7 +1636,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28">
         <v>50000</v>
@@ -1647,10 +1647,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1658,10 +1658,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1669,10 +1669,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1680,10 +1680,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1691,10 +1691,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1702,7 +1702,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -1713,10 +1713,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1724,10 +1724,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1735,10 +1735,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1746,10 +1746,10 @@
         <v>4</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1757,10 +1757,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1768,10 +1768,10 @@
         <v>4</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1779,10 +1779,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1790,10 +1790,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1801,10 +1801,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1812,10 +1812,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1823,10 +1823,10 @@
         <v>4</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1834,10 +1834,10 @@
         <v>4</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1845,10 +1845,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1856,10 +1856,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1867,10 +1867,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1878,10 +1878,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1889,10 +1889,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C51" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1900,10 +1900,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1911,10 +1911,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1922,10 +1922,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1933,7 +1933,7 @@
         <v>4</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" t="s">
         <v>87</v>
@@ -1944,7 +1944,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C56">
         <v>8906784590</v>
@@ -1955,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -1991,10 +1991,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" t="s">
         <v>190</v>
-      </c>
-      <c r="C2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2002,10 +2002,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" t="s">
         <v>192</v>
-      </c>
-      <c r="C3" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2013,7 +2013,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
         <v>87</v>
@@ -2024,7 +2024,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C5" s="9">
         <v>123456789012</v>
@@ -2035,7 +2035,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2049,7 +2049,7 @@
         <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2057,10 +2057,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" t="s">
         <v>198</v>
-      </c>
-      <c r="C8" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2068,10 +2068,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" t="s">
         <v>200</v>
-      </c>
-      <c r="C9" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2079,7 +2079,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C10">
         <v>4021</v>
@@ -2090,10 +2090,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2101,10 +2101,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2112,10 +2112,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" t="s">
         <v>204</v>
-      </c>
-      <c r="C13" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2123,10 +2123,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" t="s">
         <v>206</v>
-      </c>
-      <c r="C14" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2134,10 +2134,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" t="s">
         <v>208</v>
-      </c>
-      <c r="C15" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2145,10 +2145,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2156,10 +2156,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C17" t="s">
         <v>212</v>
-      </c>
-      <c r="C17" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" t="s">
         <v>214</v>
-      </c>
-      <c r="C18" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2178,10 +2178,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" t="s">
         <v>216</v>
-      </c>
-      <c r="C19" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20">
         <v>1234</v>
@@ -2200,10 +2200,10 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2211,10 +2211,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2222,10 +2222,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2233,10 +2233,10 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2244,10 +2244,10 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2255,7 +2255,7 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C27">
         <v>365</v>
@@ -2277,7 +2277,7 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C28">
         <v>10000</v>
@@ -2288,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C29">
         <v>10000</v>
@@ -2299,7 +2299,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C30">
         <v>10000</v>
@@ -2310,7 +2310,7 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C31">
         <v>10000</v>
@@ -2321,7 +2321,7 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C32">
         <v>10000</v>
@@ -2332,7 +2332,7 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C33">
         <v>10000</v>
@@ -2343,10 +2343,10 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
+        <v>229</v>
+      </c>
+      <c r="C34" t="s">
         <v>230</v>
-      </c>
-      <c r="C34" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2354,7 +2354,7 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C35" t="s">
         <v>35</v>
@@ -2365,10 +2365,10 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" t="s">
         <v>233</v>
-      </c>
-      <c r="C36" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2376,10 +2376,10 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2387,10 +2387,10 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2398,10 +2398,10 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2409,10 +2409,10 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2420,10 +2420,10 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2431,10 +2431,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2442,10 +2442,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2453,10 +2453,10 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2464,10 +2464,10 @@
         <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2475,7 +2475,7 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -3408,10 +3408,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" t="s">
         <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3427,5 +3427,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B62077-22A8-42B7-A065-D4237A93A44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7DB0EF-A796-49BC-9881-8D1B5B898109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="10" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7DB0EF-A796-49BC-9881-8D1B5B898109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F8EAA7-142A-4A8E-828D-078989056017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="10" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="243">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -484,12 +484,6 @@
     <t>Signature_Telephone_Number__c</t>
   </si>
   <si>
-    <t>Signature_Date__c</t>
-  </si>
-  <si>
-    <t>1 St Tier</t>
-  </si>
-  <si>
     <t>Austin Lee</t>
   </si>
   <si>
@@ -559,9 +553,6 @@
     <t>AR: Arkansas</t>
   </si>
   <si>
-    <t>4673-907</t>
-  </si>
-  <si>
     <t>Simon</t>
   </si>
   <si>
@@ -580,12 +571,6 @@
     <t>CA: California</t>
   </si>
   <si>
-    <t>34789-234</t>
-  </si>
-  <si>
-    <t>Grantee PO</t>
-  </si>
-  <si>
     <t>Johnson</t>
   </si>
   <si>
@@ -776,6 +761,12 @@
   </si>
   <si>
     <t>CongressionalDistrict1__c</t>
+  </si>
+  <si>
+    <t>46731-9074</t>
+  </si>
+  <si>
+    <t>34789-2345</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67079260-A8F8-4A08-88D9-C04C84F847B8}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
@@ -1353,7 +1344,7 @@
         <v>93</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1364,7 +1355,7 @@
         <v>94</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1375,7 +1366,7 @@
         <v>95</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1419,7 +1410,7 @@
         <v>99</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1429,8 +1420,8 @@
       <c r="B9" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C9" t="s">
-        <v>149</v>
+      <c r="C9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1441,7 +1432,7 @@
         <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1452,7 +1443,7 @@
         <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1463,7 +1454,7 @@
         <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1474,7 +1465,7 @@
         <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1485,7 +1476,7 @@
         <v>105</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1496,7 +1487,7 @@
         <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1518,7 +1509,7 @@
         <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1529,7 +1520,7 @@
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1540,7 +1531,7 @@
         <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1551,7 +1542,7 @@
         <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1562,7 +1553,7 @@
         <v>112</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1573,7 +1564,7 @@
         <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1595,7 +1586,7 @@
         <v>115</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1606,7 +1597,7 @@
         <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1628,7 +1619,7 @@
         <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1650,7 +1641,7 @@
         <v>120</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1661,7 +1652,7 @@
         <v>121</v>
       </c>
       <c r="C30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1672,7 +1663,7 @@
         <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1683,7 +1674,7 @@
         <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1694,7 +1685,7 @@
         <v>124</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1716,7 +1707,7 @@
         <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1727,7 +1718,7 @@
         <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1738,7 +1729,7 @@
         <v>128</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1749,7 +1740,7 @@
         <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1760,7 +1751,7 @@
         <v>130</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1771,7 +1762,7 @@
         <v>131</v>
       </c>
       <c r="C40" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1782,7 +1773,7 @@
         <v>132</v>
       </c>
       <c r="C41" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1793,7 +1784,7 @@
         <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1804,7 +1795,7 @@
         <v>134</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1815,7 +1806,7 @@
         <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1826,7 +1817,7 @@
         <v>136</v>
       </c>
       <c r="C45" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1837,7 +1828,7 @@
         <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1848,7 +1839,7 @@
         <v>138</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1859,7 +1850,7 @@
         <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1867,10 +1858,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C49" t="s">
-        <v>181</v>
+        <v>141</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1878,10 +1869,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>165</v>
+        <v>142</v>
+      </c>
+      <c r="C50" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1889,10 +1880,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C51" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1900,10 +1891,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C52" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1911,10 +1902,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C53" t="s">
-        <v>183</v>
+        <v>145</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1922,10 +1913,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>184</v>
+        <v>146</v>
+      </c>
+      <c r="C54" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1933,32 +1924,10 @@
         <v>4</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C55" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C56">
+      <c r="C55">
         <v>8906784590</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1991,10 +1960,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2002,10 +1971,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2013,7 +1982,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C4" t="s">
         <v>87</v>
@@ -2024,7 +1993,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C5" s="9">
         <v>123456789012</v>
@@ -2035,7 +2004,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2049,7 +2018,7 @@
         <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2057,10 +2026,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2068,10 +2037,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2079,7 +2048,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C10">
         <v>4021</v>
@@ -2090,10 +2059,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2101,10 +2070,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2112,10 +2081,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2123,10 +2092,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C14" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2134,10 +2103,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C15" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2145,10 +2114,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2156,10 +2125,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C17" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2167,10 +2136,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2178,10 +2147,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C19" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2203,7 +2172,7 @@
         <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2211,10 +2180,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C22" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2222,10 +2191,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C23" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2233,10 +2202,10 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C24" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2244,10 +2213,10 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C25" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2255,7 +2224,7 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2266,7 +2235,7 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C27">
         <v>365</v>
@@ -2277,7 +2246,7 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C28">
         <v>10000</v>
@@ -2288,7 +2257,7 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C29">
         <v>10000</v>
@@ -2299,7 +2268,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C30">
         <v>10000</v>
@@ -2310,7 +2279,7 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C31">
         <v>10000</v>
@@ -2321,7 +2290,7 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C32">
         <v>10000</v>
@@ -2332,7 +2301,7 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C33">
         <v>10000</v>
@@ -2343,10 +2312,10 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2354,7 +2323,7 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C35" t="s">
         <v>35</v>
@@ -2365,10 +2334,10 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C36" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2376,10 +2345,10 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C37" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2387,10 +2356,10 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2398,10 +2367,10 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C39" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2409,10 +2378,10 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C40" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2420,10 +2389,10 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C41" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2431,10 +2400,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C42" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2442,10 +2411,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C43" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2453,10 +2422,10 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2467,7 +2436,7 @@
         <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2475,7 +2444,7 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -3408,7 +3377,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
         <v>91</v>

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F8EAA7-142A-4A8E-828D-078989056017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EDD5ED-C062-44FF-A199-93608504028A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="10" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="242">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -311,9 +311,6 @@
   </si>
   <si>
     <t>BudgetLevel__c</t>
-  </si>
-  <si>
-    <t>1st District</t>
   </si>
   <si>
     <t>BudgetBuildupNeeded__c</t>
@@ -1305,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
         <v>88</v>
@@ -1341,10 +1338,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1352,10 +1349,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1363,10 +1360,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1374,7 +1371,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5">
         <v>2023</v>
@@ -1385,7 +1382,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1396,7 +1393,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7">
         <v>-50</v>
@@ -1407,10 +1404,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1418,7 +1415,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1429,10 +1426,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1440,10 +1437,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1451,10 +1448,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1462,10 +1459,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1473,10 +1470,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1484,10 +1481,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1495,7 +1492,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C16">
         <v>123</v>
@@ -1506,10 +1503,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1517,10 +1514,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1528,10 +1525,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1539,10 +1536,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1550,10 +1547,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1561,10 +1558,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1572,7 +1569,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C23">
         <v>456</v>
@@ -1583,10 +1580,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1594,10 +1591,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1605,7 +1602,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C26">
         <v>11.122999999999999</v>
@@ -1616,10 +1613,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1627,7 +1624,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C28">
         <v>50000</v>
@@ -1638,10 +1635,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1649,10 +1646,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1660,10 +1657,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1671,10 +1668,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1682,10 +1679,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1693,7 +1690,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C34">
         <v>23</v>
@@ -1704,10 +1701,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1715,10 +1712,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C36" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1726,10 +1723,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1737,10 +1734,10 @@
         <v>4</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1748,10 +1745,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1759,10 +1756,10 @@
         <v>4</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1770,10 +1767,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1781,10 +1778,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1792,10 +1789,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1803,10 +1800,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1814,10 +1811,10 @@
         <v>4</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1825,10 +1822,10 @@
         <v>4</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1836,10 +1833,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1847,10 +1844,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1858,10 +1855,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1869,10 +1866,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1880,10 +1877,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C51" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1891,10 +1888,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1902,10 +1899,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1913,7 +1910,7 @@
         <v>4</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
         <v>87</v>
@@ -1924,7 +1921,7 @@
         <v>4</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55">
         <v>8906784590</v>
@@ -1960,10 +1957,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" t="s">
         <v>184</v>
-      </c>
-      <c r="C2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1971,10 +1968,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" t="s">
         <v>186</v>
-      </c>
-      <c r="C3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1982,7 +1979,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
         <v>87</v>
@@ -1993,7 +1990,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C5" s="9">
         <v>123456789012</v>
@@ -2004,7 +2001,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2018,7 +2015,7 @@
         <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2026,10 +2023,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" t="s">
         <v>192</v>
-      </c>
-      <c r="C8" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2037,10 +2034,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" t="s">
         <v>194</v>
-      </c>
-      <c r="C9" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2048,7 +2045,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C10">
         <v>4021</v>
@@ -2059,10 +2056,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2070,10 +2067,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2081,10 +2078,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" t="s">
         <v>198</v>
-      </c>
-      <c r="C13" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2092,10 +2089,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" t="s">
         <v>200</v>
-      </c>
-      <c r="C14" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2103,10 +2100,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" t="s">
         <v>202</v>
-      </c>
-      <c r="C15" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2114,10 +2111,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2125,10 +2122,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" t="s">
         <v>206</v>
-      </c>
-      <c r="C17" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2136,10 +2133,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" t="s">
         <v>208</v>
-      </c>
-      <c r="C18" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2147,10 +2144,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" t="s">
         <v>210</v>
-      </c>
-      <c r="C19" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2158,7 +2155,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20">
         <v>1234</v>
@@ -2169,10 +2166,10 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2180,10 +2177,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2191,10 +2188,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2202,10 +2199,10 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2213,10 +2210,10 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2224,7 +2221,7 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2235,7 +2232,7 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C27">
         <v>365</v>
@@ -2246,7 +2243,7 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C28">
         <v>10000</v>
@@ -2257,7 +2254,7 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C29">
         <v>10000</v>
@@ -2268,7 +2265,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C30">
         <v>10000</v>
@@ -2279,7 +2276,7 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C31">
         <v>10000</v>
@@ -2290,7 +2287,7 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C32">
         <v>10000</v>
@@ -2301,7 +2298,7 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C33">
         <v>10000</v>
@@ -2312,10 +2309,10 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
+        <v>223</v>
+      </c>
+      <c r="C34" t="s">
         <v>224</v>
-      </c>
-      <c r="C34" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2323,7 +2320,7 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C35" t="s">
         <v>35</v>
@@ -2334,10 +2331,10 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" t="s">
         <v>227</v>
-      </c>
-      <c r="C36" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2345,10 +2342,10 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2356,10 +2353,10 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2367,10 +2364,10 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2378,10 +2375,10 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2389,10 +2386,10 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2400,10 +2397,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2411,10 +2408,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2422,10 +2419,10 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2433,10 +2430,10 @@
         <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2444,7 +2441,7 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -3377,10 +3374,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C6" t="s">
-        <v>91</v>
+        <v>239</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">

--- a/src/main/resources/Application_Field_Values - backup.xlsx
+++ b/src/main/resources/Application_Field_Values - backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EDD5ED-C062-44FF-A199-93608504028A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4202A592-826C-4E9B-858B-4D656B37840F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="9" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="242">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1165,11 +1165,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="43.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1247,10 +1247,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE580EF4-51C5-4146-9C7E-90A609FABAEF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
-    <col min="3" max="3" width="31.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" customWidth="1"/>
+    <col min="3" max="3" width="31.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1316,10 +1316,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67079260-A8F8-4A08-88D9-C04C84F847B8}">
   <dimension ref="A1:C55"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1935,10 +1935,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BAA1334-5A12-4B6F-A35F-258AF51C82C8}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="89.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="89.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2432,8 +2432,8 @@
       <c r="B45" t="s">
         <v>139</v>
       </c>
-      <c r="C45" t="s">
-        <v>208</v>
+      <c r="C45">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2459,10 +2459,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2606,10 +2606,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2675,10 +2675,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2755,10 +2755,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2803,10 +2803,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2971,10 +2971,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3132,10 +3132,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3168,10 +3168,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3216,10 +3216,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3308,10 +3308,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579718D7-4C36-4B54-B5F7-43B2B7C68B72}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
